--- a/Datas/PropTrap.xlsx
+++ b/Datas/PropTrap.xlsx
@@ -133,7 +133,7 @@
     <t>Small:0.8,1.0|Medium:0.4,0.8|Large:0.1,0.3|Special:0,0</t>
   </si>
   <si>
-    <t>Arts/Prefabs/Props/Traps/Trap_Bomb</t>
+    <t>Arts/Props/Prefabs/Prop_Trap</t>
   </si>
   <si>
     <t>示例</t>
@@ -1272,28 +1272,28 @@
         <v>1</v>
       </c>
       <c r="C5" s="2">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2">
+        <v>90</v>
+      </c>
+      <c r="G5" s="2">
         <v>3</v>
       </c>
-      <c r="D5" s="2">
+      <c r="H5" s="2">
+        <v>6</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
         <v>5</v>
-      </c>
-      <c r="E5" s="2">
-        <v>100</v>
-      </c>
-      <c r="F5" s="2">
-        <v>150</v>
-      </c>
-      <c r="G5" s="2">
-        <v>10</v>
-      </c>
-      <c r="H5" s="2">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2">
-        <v>2</v>
-      </c>
-      <c r="J5" s="2">
-        <v>20</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>33</v>

--- a/Datas/PropTrap.xlsx
+++ b/Datas/PropTrap.xlsx
@@ -133,7 +133,7 @@
     <t>Small:0.8,1.0|Medium:0.4,0.8|Large:0.1,0.3|Special:0,0</t>
   </si>
   <si>
-    <t>Arts/Props/Prefabs/Prop_Trap</t>
+    <t>Arts/Props/Prefabs/pf_prop_trap</t>
   </si>
   <si>
     <t>示例</t>

--- a/Datas/PropTrap.xlsx
+++ b/Datas/PropTrap.xlsx
@@ -79,7 +79,7 @@
     <t>float</t>
   </si>
   <si>
-    <t>(map#sep=:|),HuntingConfig.Enum.EVolumeType,(array#sep=,),float</t>
+    <t>(map#sep=:|),HuntingConfig.Enum.ESpecieType,(array#sep=,),float</t>
   </si>
   <si>
     <t>string</t>
@@ -130,7 +130,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>Small:0.8,1.0|Medium:0.4,0.8|Large:0.1,0.3|Special:0,0</t>
+    <t>Small:0.8,1.0|Medium:0.4,0.8|Large:0.1,0.3|Bullet:0,0|ThreeKPCoin:0,0</t>
   </si>
   <si>
     <t>Arts/Props/Prefabs/pf_prop_trap</t>

--- a/Datas/PropTrap.xlsx
+++ b/Datas/PropTrap.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -133,7 +133,7 @@
     <t>Small:0.8,1.0|Medium:0.4,0.8|Large:0.1,0.3|Bullet:0,0|ThreeKPCoin:0,0</t>
   </si>
   <si>
-    <t>Arts/Props/Prefabs/pf_prop_trap</t>
+    <t>Assets/Arts/Prefabs/Props/pf_prop_trap</t>
   </si>
   <si>
     <t>示例</t>
@@ -1267,7 +1267,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:13">
+    <row r="5" ht="28" customHeight="1" spans="2:13">
       <c r="B5" s="2">
         <v>1</v>
       </c>

--- a/Datas/PropTrap.xlsx
+++ b/Datas/PropTrap.xlsx
@@ -1275,7 +1275,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2">
         <v>20</v>
@@ -1284,16 +1284,16 @@
         <v>90</v>
       </c>
       <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
         <v>3</v>
-      </c>
-      <c r="H5" s="2">
-        <v>6</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
       </c>
       <c r="J5" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>33</v>

--- a/Datas/PropTrap.xlsx
+++ b/Datas/PropTrap.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -64,9 +64,6 @@
     <t>AttractRadiusRangeByVolume</t>
   </si>
   <si>
-    <t>TrapPrefabResourcePath</t>
-  </si>
-  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -124,16 +121,10 @@
     <t>按体型划分的吸引半径范围比例</t>
   </si>
   <si>
-    <t>陷阱预制体资源路径</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
     <t>Small:0.8,1.0|Medium:0.4,0.8|Large:0.1,0.3|Bullet:0,0|ThreeKPCoin:0,0</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Props/pf_prop_trap</t>
   </si>
   <si>
     <t>示例</t>
@@ -1094,16 +1085,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="10" width="28.625" customWidth="1"/>
     <col min="11" max="11" width="76.625" customWidth="1"/>
-    <col min="12" max="12" width="56.625" customWidth="1"/>
-    <col min="13" max="13" width="28.625" customWidth="1"/>
+    <col min="12" max="12" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:13">
+    <row r="1" ht="28" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1140,134 +1130,122 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:12">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:12">
+      <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>17</v>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:12">
+      <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>19</v>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="2:13">
+    <row r="5" ht="28" customHeight="1" spans="2:12">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -1296,13 +1274,10 @@
         <v>8</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/PropTrap.xlsx
+++ b/Datas/PropTrap.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -37,22 +37,7 @@
     <t>ID</t>
   </si>
   <si>
-    <t>TrapCount</t>
-  </si>
-  <si>
-    <t>SpawnMinDistance</t>
-  </si>
-  <si>
-    <t>SpawnMaxDistance</t>
-  </si>
-  <si>
-    <t>SpawnSectorAngle</t>
-  </si>
-  <si>
-    <t>SpawnAnimalCheckRadius</t>
-  </si>
-  <si>
-    <t>SpawnTrapMinDistance</t>
+    <t>SpawnCount</t>
   </si>
   <si>
     <t>TriggerRadius</t>
@@ -73,6 +58,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>(array#sep=,),int</t>
+  </si>
+  <si>
     <t>float</t>
   </si>
   <si>
@@ -97,21 +85,6 @@
     <t>陷阱数量</t>
   </si>
   <si>
-    <t>生成最小距离</t>
-  </si>
-  <si>
-    <t>生成最大距离</t>
-  </si>
-  <si>
-    <t>生成扇形角度</t>
-  </si>
-  <si>
-    <t>生成时检测动物半径</t>
-  </si>
-  <si>
-    <t>生成时陷阱最小间隔</t>
-  </si>
-  <si>
     <t>陷阱触发半径</t>
   </si>
   <si>
@@ -122,6 +95,9 @@
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>6,9</t>
   </si>
   <si>
     <t>Small:0.8,1.0|Medium:0.4,0.8|Large:0.1,0.3|Bullet:0,0|ThreeKPCoin:0,0</t>
@@ -1085,15 +1061,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="10" width="28.625" customWidth="1"/>
-    <col min="11" max="11" width="76.625" customWidth="1"/>
-    <col min="12" max="12" width="28.625" customWidth="1"/>
+    <col min="1" max="5" width="28.625" customWidth="1"/>
+    <col min="6" max="6" width="76.625" customWidth="1"/>
+    <col min="7" max="7" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:12">
+    <row r="1" ht="28" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1115,169 +1091,94 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="1" t="s">
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:7">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="2:12">
+    <row r="5" ht="28" customHeight="1" spans="2:7">
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
         <v>6</v>
       </c>
-      <c r="D5" s="2">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2">
-        <v>90</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2">
-        <v>3</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2">
-        <v>8</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>32</v>
+      <c r="F5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/PropTrap.xlsx
+++ b/Datas/PropTrap.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -49,9 +49,6 @@
     <t>AttractRadiusRangeByVolume</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -67,9 +64,6 @@
     <t>(map#sep=:|),HuntingConfig.Enum.ESpecieType,(array#sep=,),float</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
@@ -94,16 +88,10 @@
     <t>按体型划分的吸引半径范围比例</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
     <t>6,9</t>
   </si>
   <si>
     <t>Small:0.8,1.0|Medium:0.4,0.8|Large:0.1,0.3|Bullet:0,0|ThreeKPCoin:0,0</t>
-  </si>
-  <si>
-    <t>示例</t>
   </si>
 </sst>
 </file>
@@ -1061,15 +1049,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="6"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="5" width="28.625" customWidth="1"/>
     <col min="6" max="6" width="76.625" customWidth="1"/>
-    <col min="7" max="7" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:7">
+    <row r="1" ht="28" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1088,85 +1075,73 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:7">
-      <c r="A3" s="1" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>14</v>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="2:7">
+    <row r="5" ht="28" customHeight="1" spans="2:6">
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1175,10 +1150,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
